--- a/Advaita_TDD/ExcelFiles/PermissionsToSelect.xlsx
+++ b/Advaita_TDD/ExcelFiles/PermissionsToSelect.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="228">
   <si>
     <t>Dataset</t>
   </si>
@@ -1706,7 +1706,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88D26F4F-D66B-47E5-9200-43D268325D01}">
-  <dimension ref="A1:B94"/>
+  <dimension ref="A1:B95"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="13.453125"/>
@@ -2406,6 +2406,11 @@
     <row r="94">
       <c r="A94" t="s" s="0">
         <v>227</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
